--- a/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
@@ -10,58 +10,22 @@
     <x:sheet name="April 2025" sheetId="8" r:id="rId8"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (NEW)</x:t>
@@ -122,7 +86,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="11">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -149,12 +113,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -165,17 +123,23 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -183,20 +147,13 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="18"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -224,15 +181,15 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="14">
+  <x:borders count="15">
     <x:border/>
     <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF000000"/>
-      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
@@ -244,14 +201,14 @@
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
@@ -269,10 +226,10 @@
       <x:right style="none">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="none">
+      <x:top style="thin">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="none">
+      <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -283,13 +240,30 @@
       <x:left style="none">
         <x:color rgb="FF000000"/>
       </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thick">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="none">
+      <x:top style="thin">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="none">
+      <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -444,37 +418,37 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -483,16 +457,13 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -501,70 +472,81 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="27">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -576,20 +558,20 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -597,10 +579,14 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -864,190 +850,186 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45717</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>17</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>45735.2932291667</x:v>
       </x:c>
-      <x:c r="I6" s="12">
+      <x:c r="I6" s="13">
         <x:v>45735.2932407407</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="n">
+      <x:c r="J6" s="12" t="n">
         <x:v>1456000</x:v>
       </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="K6" s="14" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="15">
         <x:v>45735.3120601852</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s"/>
+      <x:c r="C7" s="16" t="s"/>
+      <x:c r="D7" s="16" t="s"/>
+      <x:c r="E7" s="16" t="s"/>
+      <x:c r="F7" s="16" t="s"/>
+      <x:c r="G7" s="16" t="s"/>
+      <x:c r="H7" s="16" t="s"/>
+      <x:c r="I7" s="16" t="s"/>
+      <x:c r="J7" s="16" t="s"/>
+      <x:c r="K7" s="16" t="s"/>
+      <x:c r="L7" s="16" t="s"/>
+      <x:c r="M7" s="16" t="s"/>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s"/>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="16" t="s"/>
-      <x:c r="F9" s="16" t="s"/>
+      <x:c r="B9" s="17" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C9" s="18" t="s"/>
+      <x:c r="D9" s="18" t="s"/>
+      <x:c r="E9" s="19" t="s"/>
+      <x:c r="F9" s="19" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C10" s="18" t="s"/>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="18" t="s"/>
-      <x:c r="F10" s="19" t="s">
-        <x:v>22</x:v>
+      <x:c r="B10" s="20" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C10" s="21" t="s"/>
+      <x:c r="D10" s="21" t="s"/>
+      <x:c r="E10" s="21" t="s"/>
+      <x:c r="F10" s="22" t="s">
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="20" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="21" t="s"/>
-      <x:c r="D11" s="21" t="s"/>
-      <x:c r="E11" s="21" t="s"/>
-      <x:c r="F11" s="22" t="n">
+      <x:c r="B11" s="23" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="24" t="s"/>
+      <x:c r="D11" s="24" t="s"/>
+      <x:c r="E11" s="24" t="s"/>
+      <x:c r="F11" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="23" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="24" t="s"/>
-      <x:c r="D12" s="24" t="s"/>
-      <x:c r="E12" s="24" t="s"/>
-      <x:c r="F12" s="25" t="n">
+      <x:c r="B12" s="26" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s"/>
+      <x:c r="D12" s="27" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2115,190 +2097,186 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>24</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>26</x:v>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>45761.0611805556</x:v>
       </x:c>
-      <x:c r="I6" s="26">
+      <x:c r="I6" s="29">
         <x:v>45690</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="n">
+      <x:c r="J6" s="12" t="n">
         <x:v>1459678</x:v>
       </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="K6" s="14" t="n">
         <x:v>672</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="15">
         <x:v>45761.0907638889</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s"/>
+      <x:c r="C7" s="16" t="s"/>
+      <x:c r="D7" s="16" t="s"/>
+      <x:c r="E7" s="16" t="s"/>
+      <x:c r="F7" s="16" t="s"/>
+      <x:c r="G7" s="16" t="s"/>
+      <x:c r="H7" s="16" t="s"/>
+      <x:c r="I7" s="16" t="s"/>
+      <x:c r="J7" s="16" t="s"/>
+      <x:c r="K7" s="16" t="s"/>
+      <x:c r="L7" s="16" t="s"/>
+      <x:c r="M7" s="16" t="s"/>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s"/>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="16" t="s"/>
-      <x:c r="F9" s="16" t="s"/>
+      <x:c r="B9" s="17" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C9" s="18" t="s"/>
+      <x:c r="D9" s="18" t="s"/>
+      <x:c r="E9" s="19" t="s"/>
+      <x:c r="F9" s="19" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C10" s="18" t="s"/>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="18" t="s"/>
-      <x:c r="F10" s="19" t="s">
-        <x:v>22</x:v>
+      <x:c r="B10" s="20" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C10" s="21" t="s"/>
+      <x:c r="D10" s="21" t="s"/>
+      <x:c r="E10" s="21" t="s"/>
+      <x:c r="F10" s="22" t="s">
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="20" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C11" s="21" t="s"/>
-      <x:c r="D11" s="21" t="s"/>
-      <x:c r="E11" s="21" t="s"/>
-      <x:c r="F11" s="22" t="n">
+      <x:c r="B11" s="23" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C11" s="24" t="s"/>
+      <x:c r="D11" s="24" t="s"/>
+      <x:c r="E11" s="24" t="s"/>
+      <x:c r="F11" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="23" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="24" t="s"/>
-      <x:c r="D12" s="24" t="s"/>
-      <x:c r="E12" s="24" t="s"/>
-      <x:c r="F12" s="25" t="n">
+      <x:c r="B12" s="26" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s"/>
+      <x:c r="D12" s="27" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
@@ -23,9 +23,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <x:si>
-    <x:t>{{Name}}</x:t>
+    <x:t>EVALUATOR SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WARDEE CABARABAN</x:t>
   </x:si>
   <x:si>
     <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (NEW)</x:t>
@@ -147,7 +150,7 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="18"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -181,7 +184,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="15">
+  <x:borders count="14">
     <x:border/>
     <x:border>
       <x:right style="thin">
@@ -226,10 +229,10 @@
       <x:right style="none">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
+      <x:top style="none">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="thin">
+      <x:bottom style="none">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -240,30 +243,13 @@
       <x:left style="none">
         <x:color rgb="FF000000"/>
       </x:left>
-      <x:right style="none">
+      <x:right style="thick">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
+      <x:top style="none">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
-    </x:border>
-    <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="none">
-        <x:color rgb="FF000000"/>
-      </x:left>
-      <x:right style="thick">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="thin">
+      <x:bottom style="none">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -445,10 +431,13 @@
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -457,13 +446,13 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -472,14 +461,11 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -515,38 +501,46 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -558,11 +552,7 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -570,8 +560,12 @@
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -579,15 +573,11 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -835,7 +825,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -852,7 +844,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>45717</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -913,24 +905,24 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H6" s="13">
         <x:v>45735.2932291667</x:v>
@@ -948,7 +940,7 @@
         <x:v>45735.3120601852</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
@@ -969,29 +961,27 @@
       <x:c r="M7" s="16" t="s"/>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s"/>
-      <x:c r="C8" s="9" t="s"/>
-      <x:c r="D8" s="9" t="s"/>
-      <x:c r="E8" s="9" t="s"/>
-      <x:c r="F8" s="9" t="s"/>
-      <x:c r="G8" s="9" t="s"/>
-      <x:c r="H8" s="9" t="s"/>
-      <x:c r="I8" s="9" t="s"/>
-      <x:c r="J8" s="9" t="s"/>
-      <x:c r="K8" s="9" t="s"/>
-      <x:c r="L8" s="9" t="s"/>
-      <x:c r="M8" s="9" t="s"/>
+      <x:c r="B8" s="17" t="s"/>
+      <x:c r="C8" s="17" t="s"/>
+      <x:c r="D8" s="17" t="s"/>
+      <x:c r="E8" s="17" t="s"/>
+      <x:c r="F8" s="17" t="s"/>
+      <x:c r="G8" s="17" t="s"/>
+      <x:c r="H8" s="17" t="s"/>
+      <x:c r="I8" s="17" t="s"/>
+      <x:c r="J8" s="17" t="s"/>
+      <x:c r="K8" s="17" t="s"/>
+      <x:c r="L8" s="17" t="s"/>
+      <x:c r="M8" s="17" t="s"/>
     </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="17" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="s"/>
-      <x:c r="D9" s="18" t="s"/>
-      <x:c r="E9" s="19" t="s"/>
-      <x:c r="F9" s="19" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
       <x:c r="G9" s="9" t="s"/>
       <x:c r="H9" s="9" t="s"/>
       <x:c r="I9" s="9" t="s"/>
@@ -1000,41 +990,49 @@
       <x:c r="L9" s="9" t="s"/>
       <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="20" t="s">
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="18" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C10" s="21" t="s"/>
-      <x:c r="D10" s="21" t="s"/>
-      <x:c r="E10" s="21" t="s"/>
-      <x:c r="F10" s="22" t="s">
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="21" t="s">
         <x:v>10</x:v>
       </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
+        <x:v>11</x:v>
+      </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="23" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="24" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C11" s="24" t="s"/>
-      <x:c r="D11" s="24" t="s"/>
-      <x:c r="E11" s="24" t="s"/>
-      <x:c r="F11" s="25" t="n">
+    </x:row>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="27" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="26" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C12" s="27" t="s"/>
-      <x:c r="D12" s="27" t="s"/>
-      <x:c r="E12" s="27" t="s"/>
-      <x:c r="F12" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2015,13 +2013,14 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B9:F9"/>
-    <x:mergeCell ref="B10:E10"/>
-    <x:mergeCell ref="B11:E11"/>
+  <x:mergeCells count="7">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -2082,7 +2081,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -2099,7 +2100,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>45748</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -2160,29 +2161,29 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H6" s="13">
         <x:v>45761.0611805556</x:v>
       </x:c>
-      <x:c r="I6" s="29">
+      <x:c r="I6" s="30">
         <x:v>45690</x:v>
       </x:c>
       <x:c r="J6" s="12" t="n">
@@ -2195,7 +2196,7 @@
         <x:v>45761.0907638889</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
@@ -2216,29 +2217,27 @@
       <x:c r="M7" s="16" t="s"/>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s"/>
-      <x:c r="C8" s="9" t="s"/>
-      <x:c r="D8" s="9" t="s"/>
-      <x:c r="E8" s="9" t="s"/>
-      <x:c r="F8" s="9" t="s"/>
-      <x:c r="G8" s="9" t="s"/>
-      <x:c r="H8" s="9" t="s"/>
-      <x:c r="I8" s="9" t="s"/>
-      <x:c r="J8" s="9" t="s"/>
-      <x:c r="K8" s="9" t="s"/>
-      <x:c r="L8" s="9" t="s"/>
-      <x:c r="M8" s="9" t="s"/>
+      <x:c r="B8" s="17" t="s"/>
+      <x:c r="C8" s="17" t="s"/>
+      <x:c r="D8" s="17" t="s"/>
+      <x:c r="E8" s="17" t="s"/>
+      <x:c r="F8" s="17" t="s"/>
+      <x:c r="G8" s="17" t="s"/>
+      <x:c r="H8" s="17" t="s"/>
+      <x:c r="I8" s="17" t="s"/>
+      <x:c r="J8" s="17" t="s"/>
+      <x:c r="K8" s="17" t="s"/>
+      <x:c r="L8" s="17" t="s"/>
+      <x:c r="M8" s="17" t="s"/>
     </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="17" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="s"/>
-      <x:c r="D9" s="18" t="s"/>
-      <x:c r="E9" s="19" t="s"/>
-      <x:c r="F9" s="19" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
       <x:c r="G9" s="9" t="s"/>
       <x:c r="H9" s="9" t="s"/>
       <x:c r="I9" s="9" t="s"/>
@@ -2247,41 +2246,49 @@
       <x:c r="L9" s="9" t="s"/>
       <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="20" t="s">
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="18" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C10" s="21" t="s"/>
-      <x:c r="D10" s="21" t="s"/>
-      <x:c r="E10" s="21" t="s"/>
-      <x:c r="F10" s="22" t="s">
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="21" t="s">
         <x:v>10</x:v>
       </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
+        <x:v>11</x:v>
+      </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="23" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="24" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="27" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C11" s="24" t="s"/>
-      <x:c r="D11" s="24" t="s"/>
-      <x:c r="E11" s="24" t="s"/>
-      <x:c r="F11" s="25" t="n">
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="26" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C12" s="27" t="s"/>
-      <x:c r="D12" s="27" t="s"/>
-      <x:c r="E12" s="27" t="s"/>
-      <x:c r="F12" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3262,13 +3269,14 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B9:F9"/>
-    <x:mergeCell ref="B10:E10"/>
-    <x:mergeCell ref="B11:E11"/>
+  <x:mergeCells count="7">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
@@ -875,7 +875,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -945,7 +945,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s"/>
       <x:c r="C7" s="16" t="s"/>
@@ -2131,7 +2131,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -2201,7 +2201,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s"/>
       <x:c r="C7" s="16" t="s"/>

--- a/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
@@ -23,12 +23,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>WARDEE CABARABAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (NEW)</x:t>
@@ -89,7 +125,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="11">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -134,15 +170,15 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -157,6 +193,13 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -404,27 +447,24 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -446,10 +486,13 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -465,7 +508,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -496,36 +539,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -552,15 +579,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -577,7 +604,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -877,18 +904,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -906,75 +921,87 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45735.2932291667</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45735.2932407407</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1456000</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>45735.3120601852</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s"/>
-      <x:c r="C7" s="16" t="s"/>
-      <x:c r="D7" s="16" t="s"/>
-      <x:c r="E7" s="16" t="s"/>
-      <x:c r="F7" s="16" t="s"/>
-      <x:c r="G7" s="16" t="s"/>
-      <x:c r="H7" s="16" t="s"/>
-      <x:c r="I7" s="16" t="s"/>
-      <x:c r="J7" s="16" t="s"/>
-      <x:c r="K7" s="16" t="s"/>
-      <x:c r="L7" s="16" t="s"/>
-      <x:c r="M7" s="16" t="s"/>
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="17" t="s"/>
-      <x:c r="C8" s="17" t="s"/>
-      <x:c r="D8" s="17" t="s"/>
-      <x:c r="E8" s="17" t="s"/>
-      <x:c r="F8" s="17" t="s"/>
-      <x:c r="G8" s="17" t="s"/>
-      <x:c r="H8" s="17" t="s"/>
-      <x:c r="I8" s="17" t="s"/>
-      <x:c r="J8" s="17" t="s"/>
-      <x:c r="K8" s="17" t="s"/>
-      <x:c r="L8" s="17" t="s"/>
-      <x:c r="M8" s="17" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45735.2932291667</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>45735.2932407407</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1456000</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45735.3120601852</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -992,44 +1019,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="B11" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s"/>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="16" t="s"/>
+      <x:c r="F11" s="16" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
-        <x:v>11</x:v>
+      <x:c r="B12" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="s"/>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="18" t="s"/>
+      <x:c r="F12" s="19" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="B13" s="20" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="B14" s="23" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2133,18 +2160,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2162,75 +2177,87 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45761.0611805556</x:v>
-      </x:c>
-      <x:c r="I6" s="30">
-        <x:v>45690</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1459678</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>672</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>45761.0907638889</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s"/>
-      <x:c r="C7" s="16" t="s"/>
-      <x:c r="D7" s="16" t="s"/>
-      <x:c r="E7" s="16" t="s"/>
-      <x:c r="F7" s="16" t="s"/>
-      <x:c r="G7" s="16" t="s"/>
-      <x:c r="H7" s="16" t="s"/>
-      <x:c r="I7" s="16" t="s"/>
-      <x:c r="J7" s="16" t="s"/>
-      <x:c r="K7" s="16" t="s"/>
-      <x:c r="L7" s="16" t="s"/>
-      <x:c r="M7" s="16" t="s"/>
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="17" t="s"/>
-      <x:c r="C8" s="17" t="s"/>
-      <x:c r="D8" s="17" t="s"/>
-      <x:c r="E8" s="17" t="s"/>
-      <x:c r="F8" s="17" t="s"/>
-      <x:c r="G8" s="17" t="s"/>
-      <x:c r="H8" s="17" t="s"/>
-      <x:c r="I8" s="17" t="s"/>
-      <x:c r="J8" s="17" t="s"/>
-      <x:c r="K8" s="17" t="s"/>
-      <x:c r="L8" s="17" t="s"/>
-      <x:c r="M8" s="17" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45761.0611805556</x:v>
+      </x:c>
+      <x:c r="I8" s="26">
+        <x:v>45690</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1459678</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>672</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45761.0907638889</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -2248,44 +2275,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="B11" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s"/>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="16" t="s"/>
+      <x:c r="F11" s="16" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
-        <x:v>11</x:v>
+      <x:c r="B12" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="s"/>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="18" t="s"/>
+      <x:c r="F12" s="19" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="B13" s="20" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="B14" s="23" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
@@ -23,12 +23,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>WARDEE CABARABAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XIII | March 2025</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -100,6 +103,9 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
+    <x:t>XIII | April 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>Amateur Radio Station License (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -125,7 +131,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -165,6 +171,30 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -436,14 +466,23 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -456,59 +495,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="27">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -539,71 +578,83 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -832,58 +883,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -926,81 +977,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="G8" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45735.2932291667</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="15">
         <x:v>45735.2932407407</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1456000</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>45735.3120601852</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -1019,44 +1070,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s"/>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="16" t="s"/>
-      <x:c r="F11" s="16" t="s"/>
+      <x:c r="B11" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C12" s="18" t="s"/>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="18" t="s"/>
-      <x:c r="F12" s="19" t="s">
+      <x:c r="B12" s="20" t="s">
         <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="22" t="n">
+      <x:c r="B13" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="n">
+      <x:c r="B14" s="26" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2043,7 +2094,7 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
     <x:mergeCell ref="B13:E13"/>
@@ -2088,58 +2139,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -2182,81 +2233,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="F8" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45761.0611805556</x:v>
       </x:c>
-      <x:c r="I8" s="26">
+      <x:c r="I8" s="29">
         <x:v>45690</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1459678</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>672</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>45761.0907638889</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -2275,44 +2326,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s"/>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="16" t="s"/>
-      <x:c r="F11" s="16" t="s"/>
+      <x:c r="B11" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C12" s="18" t="s"/>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="18" t="s"/>
-      <x:c r="F12" s="19" t="s">
+      <x:c r="B12" s="20" t="s">
         <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="22" t="n">
+      <x:c r="B13" s="23" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="n">
+      <x:c r="B14" s="26" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3299,7 +3350,7 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
     <x:mergeCell ref="B13:E13"/>

--- a/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -68,6 +68,42 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ApplicationType}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Name}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Status}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Address}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.PermitNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ReferenceNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DateOfFiling}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ExpirationDate}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Amount}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DatePaid}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (NEW)</x:t>
@@ -128,10 +164,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
+    <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
+    <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="15">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -176,15 +214,7 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="16"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF0000FF"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -200,15 +230,15 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -223,13 +253,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -471,21 +494,21 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -495,59 +518,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -578,84 +601,92 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -883,78 +914,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
-    <x:row r="4" spans="1:28">
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28">
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -975,7 +1018,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1015,104 +1058,141 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="C8" s="9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="D8" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="E8" s="9" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="F8" s="9" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="G8" s="9" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="15">
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>45735.2932291667</x:v>
       </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="I10" s="17">
         <x:v>45735.2932407407</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1456000</x:v>
       </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L8" s="15">
+      <x:c r="L10" s="19">
         <x:v>45735.3120601852</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="M10" s="15" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="20" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="22" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="23" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="s">
+        <x:v>36</x:v>
+      </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
-        <x:v>24</x:v>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="29" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2091,14 +2171,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -2139,78 +2220,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
-    <x:row r="4" spans="1:28">
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28">
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2231,7 +2324,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -2271,104 +2364,141 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
+      <x:c r="B8" s="9" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F8" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G8" s="9" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>45761.0611805556</x:v>
       </x:c>
-      <x:c r="I8" s="29">
+      <x:c r="I10" s="17">
         <x:v>45690</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1459678</x:v>
       </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>672</x:v>
       </x:c>
-      <x:c r="L8" s="15">
+      <x:c r="L10" s="19">
         <x:v>45761.0907638889</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+      <x:c r="M10" s="15" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="20" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="22" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="23" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="s">
+        <x:v>36</x:v>
+      </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
-        <x:v>24</x:v>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="29" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3347,14 +3477,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -68,42 +68,6 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ApplicationType}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Name}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Status}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Address}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.PermitNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ReferenceNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DateOfFiling}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ExpirationDate}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Amount}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DatePaid}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (NEW)</x:t>
@@ -169,7 +133,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -213,14 +177,6 @@
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
-      <x:sz val="16"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
@@ -235,10 +191,18 @@
       <x:family val="2"/>
     </x:font>
     <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -253,6 +217,13 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -497,16 +468,16 @@
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -518,24 +489,21 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -554,10 +522,13 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -570,7 +541,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -601,28 +572,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -637,10 +600,6 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -665,15 +624,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1018,7 +977,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1058,138 +1017,101 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="9" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="H8" s="15">
+        <x:v>45735.2932291667</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>45735.2932407407</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1456000</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45735.3120601852</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J8" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="K8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45735.2932291667</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>45735.2932407407</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1456000</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>45735.3120601852</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
+      <x:c r="B13" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="s"/>
+      <x:c r="D13" s="18" t="s"/>
+      <x:c r="E13" s="19" t="s"/>
+      <x:c r="F13" s="19" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
-        <x:v>36</x:v>
+      <x:c r="B14" s="20" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="22" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="B15" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
+      <x:c r="B16" s="26" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2291,7 +2213,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -2324,7 +2246,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -2364,138 +2286,101 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="9" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="9" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>45761.0611805556</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>45690</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1459678</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>672</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45761.0907638889</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J8" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="K8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45761.0611805556</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>45690</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1459678</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>672</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>45761.0907638889</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
+      <x:c r="B13" s="17" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="s"/>
+      <x:c r="D13" s="18" t="s"/>
+      <x:c r="E13" s="19" t="s"/>
+      <x:c r="F13" s="19" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
-        <x:v>36</x:v>
+      <x:c r="B14" s="20" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="22" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="B15" s="23" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
+      <x:c r="B16" s="26" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
@@ -1071,50 +1071,50 @@
       <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="17" t="s">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C13" s="18" t="s"/>
-      <x:c r="D13" s="18" t="s"/>
-      <x:c r="E13" s="19" t="s"/>
-      <x:c r="F13" s="19" t="s"/>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="20" t="s">
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="22" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="23" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2098,10 +2098,10 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B13:F13"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -2340,50 +2340,50 @@
       <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="17" t="s">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C13" s="18" t="s"/>
-      <x:c r="D13" s="18" t="s"/>
-      <x:c r="E13" s="19" t="s"/>
-      <x:c r="F13" s="19" t="s"/>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="20" t="s">
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="22" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="23" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3367,10 +3367,10 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B13:F13"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -88,6 +88,9 @@
     <x:t>61-3-2025-1016</x:t>
   </x:si>
   <x:si>
+    <x:t>1456000</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cherry Mae Anub</x:t>
   </x:si>
   <x:si>
@@ -122,6 +125,9 @@
   </x:si>
   <x:si>
     <x:t>61-4-2025-1163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1459678</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1038,22 +1044,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H8" s="15">
-        <x:v>45735.2932291667</x:v>
+        <x:v>45735.2932379167</x:v>
       </x:c>
       <x:c r="I8" s="15">
-        <x:v>45735.2932407407</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1456000</x:v>
+        <x:v>45735.2932451389</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
       <x:c r="K8" s="16" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="L8" s="15">
-        <x:v>45735.3120601852</x:v>
+        <x:v>45735.3120613657</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -1073,7 +1079,7 @@
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="17" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="18" t="s"/>
       <x:c r="D11" s="18" t="s"/>
@@ -1082,13 +1088,13 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
       <x:c r="B12" s="20" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C12" s="21" t="s"/>
       <x:c r="D12" s="21" t="s"/>
       <x:c r="E12" s="21" t="s"/>
       <x:c r="F12" s="22" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
@@ -1104,7 +1110,7 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
       <x:c r="B14" s="26" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C14" s="27" t="s"/>
       <x:c r="D14" s="27" t="s"/>
@@ -2213,7 +2219,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -2289,40 +2295,40 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D8" s="14" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H8" s="15">
-        <x:v>45761.0611805556</x:v>
+        <x:v>45761.0611867708</x:v>
       </x:c>
       <x:c r="I8" s="15">
         <x:v>45690</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1459678</x:v>
+      <x:c r="J8" s="14" t="s">
+        <x:v>34</x:v>
       </x:c>
       <x:c r="K8" s="16" t="n">
         <x:v>672</x:v>
       </x:c>
       <x:c r="L8" s="15">
-        <x:v>45761.0907638889</x:v>
+        <x:v>45761.0907686806</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -2342,7 +2348,7 @@
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="17" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="18" t="s"/>
       <x:c r="D11" s="18" t="s"/>
@@ -2351,18 +2357,18 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
       <x:c r="B12" s="20" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C12" s="21" t="s"/>
       <x:c r="D12" s="21" t="s"/>
       <x:c r="E12" s="21" t="s"/>
       <x:c r="F12" s="22" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
       <x:c r="B13" s="23" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C13" s="24" t="s"/>
       <x:c r="D13" s="24" t="s"/>
@@ -2373,7 +2379,7 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
       <x:c r="B14" s="26" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C14" s="27" t="s"/>
       <x:c r="D14" s="27" t="s"/>

--- a/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
@@ -983,7 +983,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1023,7 +1023,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -2252,7 +2252,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -2292,7 +2292,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>28</x:v>

--- a/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <x:si>
-    <x:t>EVALUATOR SUMMARY</x:t>
+    <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
   <x:si>
     <x:t>WARDEE CABARABAN</x:t>

--- a/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
@@ -23,15 +23,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
   <x:si>
     <x:t>WARDEE CABARABAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XIII | March 2025</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -104,9 +101,6 @@
   </x:si>
   <x:si>
     <x:t>TOTAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XIII | April 2025</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur Radio Station License (RENEWAL)</x:t>
@@ -466,7 +460,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="27">
+  <x:cellStyleXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -483,6 +477,9 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -547,7 +544,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -583,6 +580,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -949,20 +950,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45717</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -985,81 +986,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="E8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="H8" s="16">
+        <x:v>45735.2932379167</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>45735.2932451389</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45735.2932379167</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>45735.2932451389</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="s">
+      <x:c r="K8" s="17" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L8" s="16">
+        <x:v>45735.3120613657</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45735.3120613657</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -1078,44 +1079,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+      <x:c r="B11" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+      <x:c r="B13" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="B14" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2218,20 +2219,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2254,81 +2255,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="E8" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="H8" s="16">
+        <x:v>45761.0611867708</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>45690</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45761.0611867708</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>45690</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>672</x:v>
       </x:c>
-      <x:c r="L8" s="15">
+      <x:c r="L8" s="16">
         <x:v>45761.0907686806</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M8" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -2347,44 +2348,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+      <x:c r="B11" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+      <x:c r="B13" s="24" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="B14" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
+++ b/reports/service-tracking-report-WARDEE-CABARABAN-evaluator-cache-serviceTracking-WARDEE-CABARABAN-XIII-202501-202612.xlsx
@@ -133,7 +133,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -173,14 +173,6 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -460,7 +452,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="28">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -471,16 +463,13 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -492,59 +481,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -579,79 +568,75 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -953,17 +938,17 @@
       <x:c r="B5" s="12">
         <x:v>45717</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -986,80 +971,80 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="16">
+      <x:c r="H8" s="15">
         <x:v>45735.2932379167</x:v>
       </x:c>
-      <x:c r="I8" s="16">
+      <x:c r="I8" s="15">
         <x:v>45735.2932451389</x:v>
       </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="J8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L8" s="16">
+      <x:c r="L8" s="15">
         <x:v>45735.3120613657</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -1079,44 +1064,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
+      <x:c r="B11" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
+      <x:c r="B12" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
+      <x:c r="B13" s="23" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
+      <x:c r="B14" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2222,17 +2207,17 @@
       <x:c r="B5" s="12">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2255,80 +2240,80 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H8" s="16">
+      <x:c r="H8" s="15">
         <x:v>45761.0611867708</x:v>
       </x:c>
-      <x:c r="I8" s="16">
+      <x:c r="I8" s="15">
         <x:v>45690</x:v>
       </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="J8" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>672</x:v>
       </x:c>
-      <x:c r="L8" s="16">
+      <x:c r="L8" s="15">
         <x:v>45761.0907686806</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -2348,44 +2333,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
+      <x:c r="B11" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
+      <x:c r="B12" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
+      <x:c r="B13" s="23" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
+      <x:c r="B14" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
